--- a/raw_data/fecundity_data.xlsx
+++ b/raw_data/fecundity_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joegunn/Desktop/Projects/active_projects/CPB_Phenotype/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF9E4F4B-A014-AB4F-A6B3-C83E9B9C6A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDB5A58-FC03-404A-A7FA-F3EE10AB2913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31480" yWindow="500" windowWidth="28800" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8560" yWindow="500" windowWidth="25600" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25203,7 +25203,7 @@
     </row>
     <row r="822" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A822" s="5">
-        <v>45427</v>
+        <v>45426</v>
       </c>
       <c r="B822" s="6" t="s">
         <v>15</v>
